--- a/examples/US Treasury Bond Analyzer (blank).xlsx
+++ b/examples/US Treasury Bond Analyzer (blank).xlsx
@@ -65,6 +65,10 @@
     <definedName name="Y5Y">'Yield Curve'!$B$17</definedName>
     <definedName name="Y10Y">'Yield Curve'!$B$18</definedName>
     <definedName name="Y30Y">'Yield Curve'!$B$19</definedName>
+    <definedName name="AttractScore">'Recommendation'!$B$37</definedName>
+    <definedName name="ModelView">'Recommendation'!$B$39</definedName>
+    <definedName name="RateOutlook">'Recommendation'!$C$45</definedName>
+    <definedName name="AnalystOverride">'Recommendation'!$C$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -80,7 +84,7 @@
     <numFmt numFmtId="168" formatCode="0.0&quot; bps&quot;"/>
     <numFmt numFmtId="169" formatCode="#,##0.0000"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -154,8 +158,20 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F7A3D"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="006B7986"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -204,8 +220,14 @@
         <bgColor rgb="00E8EEF4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6EAD9"/>
+        <bgColor rgb="00D6EAD9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -291,11 +313,58 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00B7C2CE"/>
+      </left>
+      <right style="medium">
+        <color rgb="00B7C2CE"/>
+      </right>
+      <top style="medium">
+        <color rgb="00B7C2CE"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00B7C2CE"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00B7C2CE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00B7C2CE"/>
+      </right>
+      <top style="medium">
+        <color rgb="00B7C2CE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00B7C2CE"/>
+      </right>
+      <top style="medium">
+        <color rgb="00B7C2CE"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00B7C2CE"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -446,8 +515,21 @@
     <xf numFmtId="168" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="7" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -1374,11 +1456,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -1392,14 +1474,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FORMULA EXPLANATIONS</t>
+          <t>FORMULA &amp; CONCEPT EXPLANATIONS</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every key calculation in plain English</t>
+          <t>Every key idea in plain English - for a beginner bond analyst</t>
         </is>
       </c>
     </row>
@@ -1484,355 +1566,1331 @@
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Read this once and you can audit any number in the workbook. Each row gives the formula, what it means, and how to read it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>Concept</t>
-        </is>
-      </c>
-      <c r="C11" s="26" t="inlineStr">
+          <t>Read this once and you can understand every number in the workbook. For each concept you get the formula, a simple explanation, why a US Treasury analyst cares, how to read it, and a quick example.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Clean price</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="55" t="inlineStr">
         <is>
           <t>Formula</t>
         </is>
       </c>
-      <c r="F11" s="26" t="inlineStr">
-        <is>
-          <t>What it means</t>
-        </is>
-      </c>
-      <c r="H11" s="26" t="inlineStr">
-        <is>
-          <t>How to read it</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Clean price</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Quoted price, excludes accrued interest</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>The price you see quoted for the Treasury.</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>What you compare across bonds; accrued is added on top to get what you pay.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>The quoted market price (per 100 face)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="25" customHeight="1">
+      <c r="A13" s="55" t="inlineStr">
+        <is>
+          <t>In plain English</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Clean price is the quoted market price of the bond. It does not include the interest that has built up since the last coupon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="55" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>It is what you compare across bonds and what screens and brokers show.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="55" t="inlineStr">
+        <is>
+          <t>How to interpret</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Above 100 = premium, below 100 = discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="55" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>A note quoted at 96.50 has a clean price of 96.50 per 100 of face value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Dirty price</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>Clean price + accrued interest</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>The actual cash you pay to settle the trade (the invoice price).</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>This is the true cost and what the cash flows discount back to.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="55" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Dirty price = clean price + accrued interest</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="25" customHeight="1">
+      <c r="A20" s="55" t="inlineStr">
+        <is>
+          <t>In plain English</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Dirty price is the actual amount the buyer pays, because it includes the accrued interest owed to the seller.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="55" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>It is the real cash cost of buying the bond - the amount that changes hands on settlement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="25" customHeight="1">
+      <c r="A22" s="55" t="inlineStr">
+        <is>
+          <t>How to interpret</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Always a bit higher than the clean price between coupon dates (equal to it right after a coupon).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="55" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Clean 96.50 + accrued 0.36 = dirty 96.86 - you pay 96.86.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Accrued interest</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="55" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>(days since last coupon / days in period) x periodic coupon</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>The slice of the next coupon the seller has earned and you reimburse.</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
-          <t>Zero for a Treasury Bill (no coupons).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Yield to maturity</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Rate that makes PV of cash flows = price (Excel YIELD)</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>The annual return if you hold to maturity and reinvest coupons at that rate.</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
-          <t>The headline yield. Higher price -&gt; lower yield.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+    </row>
+    <row r="27" ht="25" customHeight="1">
+      <c r="A27" s="55" t="inlineStr">
+        <is>
+          <t>In plain English</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Accrued interest is the slice of the next coupon that the seller has already earned by holding the bond, and which you reimburse when you buy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="25" customHeight="1">
+      <c r="A28" s="55" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>It explains why you pay more than the quoted price, and it is zero for a Treasury Bill (no coupons).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="55" t="inlineStr">
+        <is>
+          <t>How to interpret</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Grows a little each day and resets to zero right after each coupon is paid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="55" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>Halfway through a semiannual period on a 4% coupon: about half of 2.0 = ~1.0 per 100.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Yield to maturity (YTM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="55" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>The rate that makes PV of cash flows = price (Excel YIELD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="25" customHeight="1">
+      <c r="A34" s="55" t="inlineStr">
+        <is>
+          <t>In plain English</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>Yield to maturity is the annual return implied by the bond's current price if you hold it to maturity and receive all payments as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="25" customHeight="1">
+      <c r="A35" s="55" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>It is the single best summary of the return you lock in today - the main number analysts compare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="25" customHeight="1">
+      <c r="A36" s="55" t="inlineStr">
+        <is>
+          <t>How to interpret</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>Higher price means lower YTM, and lower price means higher YTM. It assumes you hold to maturity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="55" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>A note at a discount (below 100) has a YTM above its coupon rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Current yield</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="55" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>Annual coupon / clean price</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>A quick income measure (coupon vs price).</t>
-        </is>
-      </c>
-      <c r="H16" s="12" t="inlineStr">
-        <is>
-          <t>Ignores capital gain/loss and timing. N/A for a Treasury Bill.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Treasury Bill yield</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>(Face / Price) ^ (1 / Years) - 1</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>A bill pays no coupon; its return is the discount from face, annualised.</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>Computed from price, face and time to maturity (effective annual).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+    </row>
+    <row r="41" ht="25" customHeight="1">
+      <c r="A41" s="55" t="inlineStr">
+        <is>
+          <t>In plain English</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>Current yield is just the annual coupon divided by the price - a quick snapshot of the income you get.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="25" customHeight="1">
+      <c r="A42" s="55" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>It shows the cash income yield, but it ignores any gain or loss versus par and the timing of cash flows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="55" t="inlineStr">
+        <is>
+          <t>How to interpret</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>Only a rough guide; YTM is the fuller measure. It is N/A for a Treasury Bill (no coupon).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="55" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>A 4% coupon bond priced at 96.50 has a current yield of 4 / 96.50 = ~4.15%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Premium / discount to par</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="55" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>Clean price - 100</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>Whether the bond trades above (premium) or below (discount) face value.</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>Coupon above current yields -&gt; premium; below -&gt; discount.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="55" t="inlineStr">
+        <is>
+          <t>In plain English</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>Whether the bond trades above par (premium) or below par (discount).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="55" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>It tells you at a glance whether the coupon is above or below current market yields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="55" t="inlineStr">
+        <is>
+          <t>How to interpret</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>Premium: coupon is higher than the yield. Discount: coupon is lower than the yield.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="55" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>Price 102 = 2-point premium; price 96.50 = 3.50-point discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>Macaulay duration</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="55" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>sum(time x PV) / sum(PV)  (Excel DURATION)</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>Weighted-average time (years) to receive the cash flows.</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>For a Treasury Bill it equals the time to maturity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+    </row>
+    <row r="55" ht="49" customHeight="1">
+      <c r="A55" s="55" t="inlineStr">
+        <is>
+          <t>In plain English</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>Macaulay duration is the weighted-average time it takes to receive the bond's cash flows. For a zero-coupon bond it is close to the time to maturity because all the cash is received at the end; for a coupon bond it is usually shorter than maturity because some cash arrives earlier through coupons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="25" customHeight="1">
+      <c r="A56" s="55" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>It is the foundation of interest-rate risk and a quick sense of how long your money is tied up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="55" t="inlineStr">
+        <is>
+          <t>How to interpret</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>Measured in years. Longer duration = the bond's cash is, on average, further away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="55" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>A 10-year Treasury note might have a Macaulay duration of ~7.5 years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>Modified duration</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>Macaulay / (1 + yield/2)  (Excel MDURATION)</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>Approximate % price change for a 1% (100 bps) yield move.</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>The main interest-rate risk number. 7 =&gt; ~7% price fall if yields rise 1%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="55" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>Macaulay duration / (1 + yield/2)  (Excel MDURATION)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="37" customHeight="1">
+      <c r="A62" s="55" t="inlineStr">
+        <is>
+          <t>In plain English</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>Modified duration shows the approximate percentage price change for a 1% (100 bps) move in yield. If modified duration is 5, then a 1% rise in yield would reduce the price by about 5%, before considering convexity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="25" customHeight="1">
+      <c r="A63" s="55" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>It is the main interest-rate risk number - how much price you can gain or lose when rates move.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="55" t="inlineStr">
+        <is>
+          <t>How to interpret</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>Bigger modified duration = more price risk. Longer bonds have larger modified duration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="A65" s="55" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>Modified duration 7.4 -&gt; a 1% yield rise cuts the price by roughly 7.4%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>Convexity</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+    </row>
+    <row r="68" ht="15" customHeight="1">
+      <c r="A68" s="55" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>sum(CF x t x (t+1)/(1+y/2)^(t+2)) / (price x 4)</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>Corrects the duration estimate because price/yield is curved.</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="inlineStr">
-        <is>
-          <t>Positive for a normal Treasury; helps on rallies, cushions sell-offs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+    </row>
+    <row r="69" ht="61" customHeight="1">
+      <c r="A69" s="55" t="inlineStr">
+        <is>
+          <t>In plain English</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>Convexity measures how much the bond's duration changes when yields move. Duration gives a straight-line estimate of price sensitivity, but bond prices do not move in a perfect straight line. Convexity improves the estimate, especially when yields move a lot. For normal fixed-rate US Treasuries, convexity is usually positive, meaning the bond gains a bit more when yields fall and loses a bit less when yields rise compared with duration-only estimates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="25" customHeight="1">
+      <c r="A70" s="55" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>It makes your price-change estimates more accurate for larger rate moves, and it is a (small) plus for holders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="A71" s="55" t="inlineStr">
+        <is>
+          <t>How to interpret</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>Positive convexity is good for you. It matters most for big yield moves and long bonds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="25" customHeight="1">
+      <c r="A72" s="55" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>For a +/-100 bps move, duration-only under-states the gain on the rally and over-states the loss on the sell-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>DV01</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="A75" s="55" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
         <is>
           <t>Modified duration x dirty price x 0.0001</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>Price change for a 1 basis-point (0.01%) yield move.</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>A price-risk measure; quoted as a positive number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Price impact from rate shocks</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>- Modified x (yield change) + 0.5 x convexity x (yield change)^2</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>Estimated % price change when the yield moves, from duration and convexity.</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
-          <t>Yields up -&gt; price down. Bigger duration -&gt; bigger move.</t>
+    </row>
+    <row r="76" ht="37" customHeight="1">
+      <c r="A76" s="55" t="inlineStr">
+        <is>
+          <t>In plain English</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>DV01 shows the approximate price change for a 1 basis-point (0.01%) move in yield. If DV01 is 45, then a 1 bp rise in yield would reduce the bond value by about 45, while a 1 bp fall would increase it by about 45. It turns duration risk into money terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="25" customHeight="1">
+      <c r="A77" s="55" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>It converts abstract duration into a concrete price/dollar risk per 1 bp - useful for sizing and hedging.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="55" t="inlineStr">
+        <is>
+          <t>How to interpret</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>Quoted as a positive number. Bigger DV01 = more price risk per basis point.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="55" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>DV01 of 0.07 per 100 face means ~0.07 price move for each 1 bp change in yield.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Rate shock analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="15" customHeight="1">
+      <c r="A82" s="55" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>price change ~ -Modified x (dy) + 0.5 x convexity x (dy)^2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="25" customHeight="1">
+      <c r="A83" s="55" t="inlineStr">
+        <is>
+          <t>In plain English</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>A rate shock estimates how the price would change if the yield jumped up or down by a set amount, using duration (the straight-line part) plus convexity (the curve correction).</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="25" customHeight="1">
+      <c r="A84" s="55" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>It stress-tests the bond so you can see the downside if rates rise and the upside if they fall.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1">
+      <c r="A85" s="55" t="inlineStr">
+        <is>
+          <t>How to interpret</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t>Yields up -&gt; price down; yields down -&gt; price up. Longer-duration bonds move more.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="15" customHeight="1">
+      <c r="A86" s="55" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="B86" s="12" t="inlineStr">
+        <is>
+          <t>+100 bps on a 7.4-duration bond: roughly -7.4% from duration, softened a little by convexity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>Yield curve</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1">
+      <c r="A89" s="55" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>Treasury yields plotted by maturity (3m, 2y, 5y, 10y, 30y)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="25" customHeight="1">
+      <c r="A90" s="55" t="inlineStr">
+        <is>
+          <t>In plain English</t>
+        </is>
+      </c>
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>The yield curve shows the yield you can earn at different maturities. It is the map of interest rates across time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="25" customHeight="1">
+      <c r="A91" s="55" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>It tells you whether longer bonds pay you more (normal) and where your bond sits versus other maturities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" s="55" t="inlineStr">
+        <is>
+          <t>How to interpret</t>
+        </is>
+      </c>
+      <c r="B92" s="12" t="inlineStr">
+        <is>
+          <t>Normal = upward-sloping (longer = higher yield). Flat = roughly level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="15" customHeight="1">
+      <c r="A93" s="55" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>If the 2y is 4.1% and the 10y is 4.5%, the curve is normal and upward-sloping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>Inverted yield curve</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="15" customHeight="1">
+      <c r="A96" s="55" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>Short-term yields higher than long-term yields (e.g. 2y &gt; 10y)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="25" customHeight="1">
+      <c r="A97" s="55" t="inlineStr">
+        <is>
+          <t>In plain English</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>An inverted curve is when short maturities yield MORE than long maturities - the opposite of normal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="15" customHeight="1">
+      <c r="A98" s="55" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="B98" s="12" t="inlineStr">
+        <is>
+          <t>It is watched closely because inversions have often (not always) preceded recessions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="15" customHeight="1">
+      <c r="A99" s="55" t="inlineStr">
+        <is>
+          <t>How to interpret</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="inlineStr">
+        <is>
+          <t>Inverted (downward-sloping) can signal that markets expect rate cuts / a slowdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1">
+      <c r="A100" s="55" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>If the 2y is 4.6% and the 10y is 4.3%, the curve is inverted by 30 bps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>Treasury bill / zero-coupon bond</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="15" customHeight="1">
+      <c r="A103" s="55" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="B103" s="10" t="inlineStr">
+        <is>
+          <t>Yield = (Face / Price)^(1/Years) - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="25" customHeight="1">
+      <c r="A104" s="55" t="inlineStr">
+        <is>
+          <t>In plain English</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>A Treasury Bill (or any zero-coupon bond) pays no coupons. You buy it below face value and get 100 back at maturity; the whole return is the discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="15" customHeight="1">
+      <c r="A105" s="55" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>Bills are short, simple and very liquid - a common place to park cash with little rate risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="15" customHeight="1">
+      <c r="A106" s="55" t="inlineStr">
+        <is>
+          <t>How to interpret</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>Accrued interest is zero, and the duration is essentially the time to maturity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="15" customHeight="1">
+      <c r="A107" s="55" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>Buy a 1-year bill at 96, get 100 at maturity -&gt; return of about 4.2%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Benchmark Treasury yield</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="15" customHeight="1">
+      <c r="A110" s="55" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="B110" s="10" t="inlineStr">
+        <is>
+          <t>The yield of a similar-maturity Treasury you compare against</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="25" customHeight="1">
+      <c r="A111" s="55" t="inlineStr">
+        <is>
+          <t>In plain English</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>The benchmark yield is the reference rate for a bond of similar maturity - usually the on-the-run (most recent) Treasury.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="25" customHeight="1">
+      <c r="A112" s="55" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>It is the yardstick for judging whether your bond's yield is high, low or fair for its maturity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="15" customHeight="1">
+      <c r="A113" s="55" t="inlineStr">
+        <is>
+          <t>How to interpret</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>Compare your bond's YTM to this benchmark to see if you are paid more or less.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="15" customHeight="1">
+      <c r="A114" s="55" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="B114" s="12" t="inlineStr">
+        <is>
+          <t>If the 10y benchmark is 4.30% and your note yields 4.48%, you earn 18 bps more.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>Spread versus benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="15" customHeight="1">
+      <c r="A117" s="55" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="B117" s="10" t="inlineStr">
+        <is>
+          <t>Spread = YTM - benchmark yield  (in bps = x 10000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="25" customHeight="1">
+      <c r="A118" s="55" t="inlineStr">
+        <is>
+          <t>In plain English</t>
+        </is>
+      </c>
+      <c r="B118" s="12" t="inlineStr">
+        <is>
+          <t>The spread is the extra yield your bond offers over the benchmark Treasury of similar maturity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="25" customHeight="1">
+      <c r="A119" s="55" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>For a Treasury it is usually small; a positive spread can mean the bond is a touch cheap (e.g. off-the-run).</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="15" customHeight="1">
+      <c r="A120" s="55" t="inlineStr">
+        <is>
+          <t>How to interpret</t>
+        </is>
+      </c>
+      <c r="B120" s="12" t="inlineStr">
+        <is>
+          <t>Positive = you earn more than the benchmark; negative = you earn less.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="15" customHeight="1">
+      <c r="A121" s="55" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>A +18 bps spread means 0.18% more yield than the benchmark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>Investment attractiveness score</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="15" customHeight="1">
+      <c r="A124" s="55" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t>Total of 5 simple category scores, out of 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="37" customHeight="1">
+      <c r="A125" s="55" t="inlineStr">
+        <is>
+          <t>In plain English</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>A simple, transparent score that adds up points for yield, low duration risk, low price sensitivity, a helpful curve, and Treasury liquidity. It is a starting point, not a personalised recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="25" customHeight="1">
+      <c r="A126" s="55" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="B126" s="12" t="inlineStr">
+        <is>
+          <t>It gives a consistent, explainable first read on whether a bond looks attractive - without pretending to know your situation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="15" customHeight="1">
+      <c r="A127" s="55" t="inlineStr">
+        <is>
+          <t>How to interpret</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t>8-10 = Attractive, 5-7 = Neutral, 0-4 = Not Attractive. The analyst can override it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="15" customHeight="1">
+      <c r="A128" s="55" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="B128" s="12" t="inlineStr">
+        <is>
+          <t>A bond scoring 8/10 (good yield, moderate duration, liquid) shows as 'Attractive'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>Buy / Hold / Avoid recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="15" customHeight="1">
+      <c r="A131" s="55" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="B131" s="10" t="inlineStr">
+        <is>
+          <t>A manual analyst decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="25" customHeight="1">
+      <c r="A132" s="55" t="inlineStr">
+        <is>
+          <t>In plain English</t>
+        </is>
+      </c>
+      <c r="B132" s="12" t="inlineStr">
+        <is>
+          <t>The final trading call. The model gives hints and an attractiveness score, but the Buy/Hold/Avoid decision is left to you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="15" customHeight="1">
+      <c r="A133" s="55" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="inlineStr">
+        <is>
+          <t>It keeps a human in the loop - the model informs the decision but does not make it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="15" customHeight="1">
+      <c r="A134" s="55" t="inlineStr">
+        <is>
+          <t>How to interpret</t>
+        </is>
+      </c>
+      <c r="B134" s="12" t="inlineStr">
+        <is>
+          <t>Combine the attractiveness view, your rate outlook and your own constraints to decide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="15" customHeight="1">
+      <c r="A135" s="55" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="B135" s="12" t="inlineStr">
+        <is>
+          <t>Attractive score + you expect yields to fall -&gt; you might lean Buy; you still decide.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="57">
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="F11:G11"/>
+  <mergeCells count="113">
+    <mergeCell ref="B61:J61"/>
+    <mergeCell ref="B14:J14"/>
+    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="B69:J69"/>
+    <mergeCell ref="B78:J78"/>
+    <mergeCell ref="B112:J112"/>
+    <mergeCell ref="A130:J130"/>
+    <mergeCell ref="B127:J127"/>
+    <mergeCell ref="B40:J40"/>
+    <mergeCell ref="B49:J49"/>
+    <mergeCell ref="B55:J55"/>
+    <mergeCell ref="B64:J64"/>
+    <mergeCell ref="B33:J33"/>
+    <mergeCell ref="B104:J104"/>
+    <mergeCell ref="B51:J51"/>
+    <mergeCell ref="B63:J63"/>
+    <mergeCell ref="B26:J26"/>
+    <mergeCell ref="B41:J41"/>
+    <mergeCell ref="B35:J35"/>
+    <mergeCell ref="B106:J106"/>
+    <mergeCell ref="B16:J16"/>
+    <mergeCell ref="B90:J90"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="B131:J131"/>
+    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="A95:J95"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="B117:J117"/>
+    <mergeCell ref="B132:J132"/>
+    <mergeCell ref="A81:J81"/>
+    <mergeCell ref="B119:J119"/>
+    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="B103:J103"/>
+    <mergeCell ref="B37:J37"/>
+    <mergeCell ref="A67:J67"/>
+    <mergeCell ref="B84:J84"/>
+    <mergeCell ref="B118:J118"/>
+    <mergeCell ref="A60:J60"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="A123:J123"/>
+    <mergeCell ref="B89:J89"/>
+    <mergeCell ref="B79:J79"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="B97:J97"/>
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="B54:J54"/>
+    <mergeCell ref="B72:J72"/>
+    <mergeCell ref="B134:J134"/>
+    <mergeCell ref="B121:J121"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="B56:J56"/>
+    <mergeCell ref="B71:J71"/>
+    <mergeCell ref="B105:J105"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="B43:J43"/>
+    <mergeCell ref="B58:J58"/>
+    <mergeCell ref="B120:J120"/>
+    <mergeCell ref="B98:J98"/>
+    <mergeCell ref="B42:J42"/>
+    <mergeCell ref="B107:J107"/>
+    <mergeCell ref="B57:J57"/>
+    <mergeCell ref="B44:J44"/>
+    <mergeCell ref="B19:J19"/>
+    <mergeCell ref="B34:J34"/>
+    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="B99:J99"/>
+    <mergeCell ref="B83:J83"/>
+    <mergeCell ref="B92:J92"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="B124:J124"/>
+    <mergeCell ref="B20:J20"/>
+    <mergeCell ref="B133:J133"/>
+    <mergeCell ref="A88:J88"/>
+    <mergeCell ref="B85:J85"/>
+    <mergeCell ref="B126:J126"/>
+    <mergeCell ref="B75:J75"/>
+    <mergeCell ref="B135:J135"/>
+    <mergeCell ref="B47:J47"/>
+    <mergeCell ref="B62:J62"/>
+    <mergeCell ref="B125:J125"/>
+    <mergeCell ref="A74:J74"/>
+    <mergeCell ref="B96:J96"/>
+    <mergeCell ref="B70:J70"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="A116:J116"/>
     <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="B111:J111"/>
+    <mergeCell ref="A53:J53"/>
+    <mergeCell ref="A109:J109"/>
+    <mergeCell ref="B82:J82"/>
+    <mergeCell ref="A102:J102"/>
+    <mergeCell ref="B128:J128"/>
+    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="B65:J65"/>
+    <mergeCell ref="B68:J68"/>
+    <mergeCell ref="A11:J11"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="B114:J114"/>
+    <mergeCell ref="B36:J36"/>
+    <mergeCell ref="B76:J76"/>
+    <mergeCell ref="B50:J50"/>
+    <mergeCell ref="B110:J110"/>
+    <mergeCell ref="B113:J113"/>
+    <mergeCell ref="B91:J91"/>
+    <mergeCell ref="B100:J100"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="B93:J93"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="B77:J77"/>
+    <mergeCell ref="B21:J21"/>
+    <mergeCell ref="B86:J86"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
@@ -2219,9 +3277,9 @@
           <t>Convexity positive?</t>
         </is>
       </c>
-      <c r="B20" s="51" t="inlineStr"/>
-      <c r="C20" s="51" t="inlineStr"/>
-      <c r="D20" s="51" t="inlineStr"/>
+      <c r="B20" s="56" t="inlineStr"/>
+      <c r="C20" s="56" t="inlineStr"/>
+      <c r="D20" s="56" t="inlineStr"/>
       <c r="E20" s="22">
         <f>IF(Convexity&gt;0,"Pass","Fail")</f>
         <v/>
@@ -2266,9 +3324,9 @@
           <t>Date order</t>
         </is>
       </c>
-      <c r="B22" s="51" t="inlineStr"/>
-      <c r="C22" s="51" t="inlineStr"/>
-      <c r="D22" s="51" t="inlineStr"/>
+      <c r="B22" s="56" t="inlineStr"/>
+      <c r="C22" s="56" t="inlineStr"/>
+      <c r="D22" s="56" t="inlineStr"/>
       <c r="E22" s="22">
         <f>IF(Settle&lt;Maturity,"Pass","Fail")</f>
         <v/>
@@ -2285,9 +3343,9 @@
           <t>No negative times</t>
         </is>
       </c>
-      <c r="B23" s="51" t="inlineStr"/>
-      <c r="C23" s="51" t="inlineStr"/>
-      <c r="D23" s="51" t="inlineStr"/>
+      <c r="B23" s="56" t="inlineStr"/>
+      <c r="C23" s="56" t="inlineStr"/>
+      <c r="D23" s="56" t="inlineStr"/>
       <c r="E23" s="22">
         <f>IF(YearsToMat&gt;0,"Pass","Fail")</f>
         <v/>
@@ -2304,9 +3362,9 @@
           <t>Frequency correct</t>
         </is>
       </c>
-      <c r="B24" s="51" t="inlineStr"/>
-      <c r="C24" s="51" t="inlineStr"/>
-      <c r="D24" s="51" t="inlineStr"/>
+      <c r="B24" s="56" t="inlineStr"/>
+      <c r="C24" s="56" t="inlineStr"/>
+      <c r="D24" s="56" t="inlineStr"/>
       <c r="E24" s="22">
         <f>IF(SecType="Treasury Bill",IF(IsZero=1,"Pass","Fail"),IF(Freq=2,"Pass","Fail"))</f>
         <v/>
@@ -2323,9 +3381,9 @@
           <t>Consistency check</t>
         </is>
       </c>
-      <c r="B25" s="51" t="inlineStr"/>
-      <c r="C25" s="51" t="inlineStr"/>
-      <c r="D25" s="51" t="inlineStr"/>
+      <c r="B25" s="56" t="inlineStr"/>
+      <c r="C25" s="56" t="inlineStr"/>
+      <c r="D25" s="56" t="inlineStr"/>
       <c r="E25" s="22">
         <f>IF(FreqWarn="OK","Pass","Fail")</f>
         <v/>
@@ -2342,9 +3400,9 @@
           <t>Coupon count</t>
         </is>
       </c>
-      <c r="B26" s="51" t="inlineStr"/>
-      <c r="C26" s="51" t="inlineStr"/>
-      <c r="D26" s="51" t="inlineStr"/>
+      <c r="B26" s="56" t="inlineStr"/>
+      <c r="C26" s="56" t="inlineStr"/>
+      <c r="D26" s="56" t="inlineStr"/>
       <c r="E26" s="22">
         <f>IF(IsZero=1,IF(Ncoup=1,"Pass","Warning"),IF(Ncoup&gt;0,"Pass","Fail"))</f>
         <v/>
@@ -2361,9 +3419,9 @@
           <t>Price vs par direction</t>
         </is>
       </c>
-      <c r="B27" s="51" t="inlineStr"/>
-      <c r="C27" s="51" t="inlineStr"/>
-      <c r="D27" s="51" t="inlineStr"/>
+      <c r="B27" s="56" t="inlineStr"/>
+      <c r="C27" s="56" t="inlineStr"/>
+      <c r="D27" s="56" t="inlineStr"/>
       <c r="E27" s="22">
         <f>IF(IsZero=1,"n/a",IF(ABS(CouponRate-YTM)&lt;0.0005,"Pass",IF(SIGN(CouponRate-YTM)=SIGN(MktClean-Face),"Pass","Fail")))</f>
         <v/>
@@ -2380,9 +3438,9 @@
           <t>Duration positive</t>
         </is>
       </c>
-      <c r="B28" s="51" t="inlineStr"/>
-      <c r="C28" s="51" t="inlineStr"/>
-      <c r="D28" s="51" t="inlineStr"/>
+      <c r="B28" s="56" t="inlineStr"/>
+      <c r="C28" s="56" t="inlineStr"/>
+      <c r="D28" s="56" t="inlineStr"/>
       <c r="E28" s="22">
         <f>IF(ModDur&gt;0,"Pass","Fail")</f>
         <v/>
@@ -2399,9 +3457,9 @@
           <t>DV01 positive</t>
         </is>
       </c>
-      <c r="B29" s="51" t="inlineStr"/>
-      <c r="C29" s="51" t="inlineStr"/>
-      <c r="D29" s="51" t="inlineStr"/>
+      <c r="B29" s="56" t="inlineStr"/>
+      <c r="C29" s="56" t="inlineStr"/>
+      <c r="D29" s="56" t="inlineStr"/>
       <c r="E29" s="22">
         <f>IF(DV01&gt;0,"Pass","Fail")</f>
         <v/>
@@ -7991,15 +9049,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -8097,25 +9155,25 @@
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>A one-page summary of price, yield, duration and curve context. The hints below are automatic; the final Buy / Hold / Avoid call is yours (a manual input).</t>
+          <t>A one-page summary of price, yield, duration and curve context, plus a simple Investment Attractiveness View. The hints and score are automatic; the final views (Buy/Hold/Avoid and Attractive/Neutral/Not Attractive) are yours to set.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Recommendation</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
+          <t>Recommendation (Buy/Hold/Avoid)</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Hold</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Your call. Use the summary and hints below to justify it.</t>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Your trading call - manual.</t>
         </is>
       </c>
     </row>
@@ -8300,7 +9358,7 @@
     </row>
     <row r="24">
       <c r="A24" s="10">
-        <f>IF(ModDur&lt;3,"Rate sensitivity: LOW (short duration) - suits an investor wanting little rate risk.",IF(ModDur&lt;8,"Rate sensitivity: MODERATE (intermediate duration).","Rate sensitivity: HIGH (long duration) - big price moves if yields change."))</f>
+        <f>IF(ModDur&lt;3,"Rate sensitivity: LOW (short duration) - little price risk if yields move.",IF(ModDur&lt;8,"Rate sensitivity: MODERATE (intermediate duration).","Rate sensitivity: HIGH (long duration) - big price moves if yields change."))</f>
         <v/>
       </c>
     </row>
@@ -8310,105 +9368,406 @@
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="10">
-        <f>IF(N(Y10Y)=0,"Add curve yields on the Yield Curve sheet for curve context.",IF(Y10Y-Y2Y&lt;-0.001,"Curve is inverted - long bonds yield less than short; weigh reinvestment vs price risk.","Curve is normal/flat - longer maturities generally offer more yield for more duration risk."))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Guidance</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>-  A short-duration Treasury (or a bill) suits an investor who wants low interest-rate sensitivity and liquidity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>-  A long-duration Treasury suits an investor who expects yields to FALL (prices would rise more).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>-  A long Treasury bond carries higher price risk if yields RISE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Analyst view (manual)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>INVESTMENT ATTRACTIVENESS VIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>What this view is (and is not)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="37" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Is this bond a good investment? This is a SIMPLE, transparent score based only on the bond's yield, duration/rate risk, price sensitivity, curve context and the fact that it is a liquid Treasury. It cannot know your personal situation - use it as a starting point, not an answer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="C31" s="27" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="D31" s="26" t="inlineStr">
+        <is>
+          <t>How it is scored</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Yield attractiveness</t>
+        </is>
+      </c>
+      <c r="B32" s="19">
+        <f>IF(YTM&gt;=0.045,3,IF(YTM&gt;=0.035,2,IF(YTM&gt;=0.025,1,0)))</f>
+        <v/>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>/ 3</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>3 if YTM &gt;= 4.5%, 2 if &gt;= 3.5%, 1 if &gt;= 2.5%, else 0 (higher yield = more income).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Duration / rate risk</t>
+        </is>
+      </c>
+      <c r="B33" s="19">
+        <f>IF(ModDur&lt;=3,3,IF(ModDur&lt;=7,2,IF(ModDur&lt;=12,1,0)))</f>
+        <v/>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>/ 3</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>Lower duration scores higher (less rate risk): 3 if &lt;= 3, 2 if &lt;= 7, 1 if &lt;= 12, else 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Main risks</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr"/>
-      <c r="C34" s="50" t="n"/>
-      <c r="D34" s="50" t="n"/>
-      <c r="E34" s="50" t="n"/>
-      <c r="F34" s="14" t="n"/>
-    </row>
-    <row r="35" ht="28" customHeight="1">
+          <t>Price sensitivity (DV01)</t>
+        </is>
+      </c>
+      <c r="B34" s="19">
+        <f>IF(DV01&lt;=0.03,2,IF(DV01&lt;=0.08,1,0))</f>
+        <v/>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>/ 2</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>Lower DV01 = smaller price move per 1 bp: 2 if &lt;= 0.03, 1 if &lt;= 0.08, else 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
+          <t>Yield curve context</t>
+        </is>
+      </c>
+      <c r="B35" s="19">
+        <f>IF(N(Y10Y)=0,0,IF(Y10Y&gt;Y2Y,1,0))</f>
+        <v/>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>/ 1</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>1 if the curve is normal/upward (positive roll-down); 0 if flat/inverted or no curve entered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Liquidity / simplicity</t>
+        </is>
+      </c>
+      <c r="B36" s="19">
+        <f>1</f>
+        <v/>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>/ 1</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>US Treasuries are highly liquid and simple, so this scores 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>TOTAL SCORE</t>
+        </is>
+      </c>
+      <c r="B37" s="50">
+        <f>SUM(B32:B36)</f>
+        <v/>
+      </c>
+      <c r="C37" s="51" t="inlineStr">
+        <is>
+          <t>/ 10</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>8-10 = Attractive,  5-7 = Neutral,  0-4 = Not Attractive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Model suggests</t>
+        </is>
+      </c>
+      <c r="B39" s="52">
+        <f>IF(AttractScore&gt;=8,"Attractive",IF(AttractScore&gt;=5,"Neutral","Not Attractive"))</f>
+        <v/>
+      </c>
+      <c r="C39" s="53" t="n"/>
+      <c r="D39" s="10">
+        <f>"Score "&amp;AttractScore&amp;" / 10"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Main reason</t>
+        </is>
+      </c>
+      <c r="B40" s="10">
+        <f>IF(AttractScore&gt;=8,"Attractive because the yield is reasonable and the rate risk is manageable.",IF(AttractScore&gt;=5,IF(ModDur&gt;7,"Neutral because the yield is acceptable, but price sensitivity to rates is high.","Neutral because the yield and the rate risk are broadly balanced."),"Not attractive because the yield does not compensate enough for the duration / rate risk."))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Key supporting factor</t>
+        </is>
+      </c>
+      <c r="B41" s="10">
+        <f>IF(YTM&gt;=0.04,"Yield of "&amp;TEXT(YTM,"0.00%")&amp;" gives reasonable income for a government bond.",IF(ModDur&lt;=3,"Low rate risk - modified duration is only "&amp;TEXT(ModDur,"0.0")&amp;".","Highly liquid, simple, default-free US Treasury exposure."))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Key risk</t>
+        </is>
+      </c>
+      <c r="B42" s="10">
+        <f>IF(ModDur&gt;7,"High duration ("&amp;TEXT(ModDur,"0.0")&amp;") - the price falls a lot if yields rise.",IF(YTM&lt;0.03,"Low yield - limited income for the interest-rate risk taken.",IF(AND(N(Y10Y)&gt;0,Y10Y&lt;Y2Y),"Inverted curve - a possible macro / recession signal.","Interest-rate risk - the price moves opposite to yields.")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Your rate outlook (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Rate outlook</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>Expect yields to stay stable</t>
+        </is>
+      </c>
+      <c r="D45" s="54" t="n"/>
+      <c r="E45" s="54" t="n"/>
+      <c r="F45" s="14" t="n"/>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>What that implies</t>
+        </is>
+      </c>
+      <c r="B46" s="10">
+        <f>IF(RateOutlook="Expect yields to rise","If yields rise, SHORTER-duration bonds are usually more attractive (less price loss). This bond has a modified duration of "&amp;TEXT(ModDur,"0.0")&amp;".",IF(RateOutlook="Expect yields to fall","If yields fall, LONGER-duration bonds usually gain more. This bond has a modified duration of "&amp;TEXT(ModDur,"0.0")&amp;".","If yields stay stable, the yield you earn (carry) matters most. This bond has a YTM of "&amp;TEXT(YTM,"0.00%")&amp;"."))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Analyst override &amp; final view</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>Analyst override</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>Use model view</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="n"/>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>Override the model if you disagree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Final investment view</t>
+        </is>
+      </c>
+      <c r="B50" s="52">
+        <f>IF(AnalystOverride="Use model view",ModelView,AnalystOverride)</f>
+        <v/>
+      </c>
+      <c r="C50" s="53" t="n"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Final output</t>
+        </is>
+      </c>
+      <c r="B52" s="11">
+        <f>"Based on this simple framework, this bond currently appears: "&amp;ModelView&amp;"."</f>
+        <v/>
+      </c>
+      <c r="C52" s="43" t="n"/>
+      <c r="D52" s="43" t="n"/>
+      <c r="E52" s="43" t="n"/>
+      <c r="F52" s="23" t="n"/>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
           <t>Final analyst comment</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr"/>
-      <c r="C35" s="50" t="n"/>
-      <c r="D35" s="50" t="n"/>
-      <c r="E35" s="50" t="n"/>
-      <c r="F35" s="14" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Reminder: this is a decision-support summary, not investment advice.</t>
+      <c r="B54" s="13" t="inlineStr"/>
+      <c r="C54" s="54" t="n"/>
+      <c r="D54" s="54" t="n"/>
+      <c r="E54" s="54" t="n"/>
+      <c r="F54" s="14" t="n"/>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="37" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>This is not a guaranteed investment recommendation. It is a structured view based on the bond's yield, duration, price sensitivity, and market-rate assumptions. A bond may be attractive for one investor and unsuitable for another depending on investment horizon, liquidity needs, and rate outlook.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="D11:F11"/>
+  <mergeCells count="37">
     <mergeCell ref="D13:F13"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="A56:F56"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="B42:F42"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A8:F8"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D33:F33"/>
     <mergeCell ref="A29:F29"/>
+    <mergeCell ref="C49:D49"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A28:F28"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="C45:F45"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="D34:F34"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B41:F41"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A25:F25"/>
-    <mergeCell ref="B35:F35"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+  <conditionalFormatting sqref="B39">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"Attractive"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"Neutral"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"Not Attractive"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B50">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
+      <formula>"Attractive"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="1">
+      <formula>"Neutral"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
+      <formula>"Not Attractive"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation sqref="C11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Buy,Hold,Avoid"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"Expect yields to rise,Expect yields to fall,Expect yields to stay stable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C49" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"Use model view,Attractive,Neutral,Not Attractive"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
